--- a/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt2_nucleos.xlsx
@@ -679,13 +679,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D3C35E2-6349-4CDD-9652-A1FEC6A6DA22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EAAD1EB-8732-4E3C-9364-950A5E5E0B4E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5C051B4-CBFF-4B3C-BF73-035394901697}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84DEF583-435B-4264-A7C1-DC160DE4B54D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA61B0BB-2E7F-4B7C-AB7B-5ED7BA284DBC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ABF905C-21F8-4E2D-A815-A075C9E08EDE}"/>
 </file>